--- a/data/trans_orig/P05A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193709</t>
+          <t>192112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>235314</t>
+          <t>236615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138778</t>
+          <t>140576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>175268</t>
+          <t>177310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344547</t>
+          <t>344416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404945</t>
+          <t>401638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138609</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180217</t>
+          <t>181596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94806</t>
+          <t>93892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129258</t>
+          <t>129977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242231</t>
+          <t>243962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300067</t>
+          <t>300406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>49746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79633</t>
+          <t>80867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32936</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61329</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90416</t>
+          <t>90044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>130171</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195649</t>
+          <t>195622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238668</t>
+          <t>237204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>146214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181547</t>
+          <t>185171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349502</t>
+          <t>349302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409486</t>
+          <t>408244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132929</t>
+          <t>131714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174838</t>
+          <t>172042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101084</t>
+          <t>98575</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137843</t>
+          <t>134768</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240539</t>
+          <t>241302</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>301085</t>
+          <t>300652</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36905</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63643</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>42500</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72121</t>
+          <t>70140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85830</t>
+          <t>87166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126470</t>
+          <t>126108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299380</t>
+          <t>301195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>352692</t>
+          <t>350981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122473</t>
+          <t>121495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>154789</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431850</t>
+          <t>433739</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>494311</t>
+          <t>495154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182000</t>
+          <t>182212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230814</t>
+          <t>229559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>62497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>94138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255744</t>
+          <t>257006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311041</t>
+          <t>314235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81276</t>
+          <t>79441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118841</t>
+          <t>120175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>30733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55248</t>
+          <t>56149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117481</t>
+          <t>116290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163451</t>
+          <t>161527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>575848</t>
+          <t>572610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>642394</t>
+          <t>640429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>369106</t>
+          <t>368250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>428181</t>
+          <t>426739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>966931</t>
+          <t>960093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1055858</t>
+          <t>1053085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373800</t>
+          <t>378155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>441140</t>
+          <t>442055</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>228604</t>
+          <t>231052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>284917</t>
+          <t>286019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>620383</t>
+          <t>623576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>707013</t>
+          <t>709395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114511</t>
+          <t>113606</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>161290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92728</t>
+          <t>90558</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>132077</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215373</t>
+          <t>215057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274277</t>
+          <t>273993</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270662</t>
+          <t>271248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315107</t>
+          <t>316006</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>395700</t>
+          <t>394099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>451007</t>
+          <t>451397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679980</t>
+          <t>681031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>750970</t>
+          <t>758020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141515</t>
+          <t>141783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184092</t>
+          <t>184363</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>202164</t>
+          <t>205943</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255707</t>
+          <t>260708</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>362794</t>
+          <t>356986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>429131</t>
+          <t>425789</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>40155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67885</t>
+          <t>67269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123253</t>
+          <t>123375</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133726</t>
+          <t>134472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180155</t>
+          <t>181656</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118700</t>
+          <t>117310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150966</t>
+          <t>149814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>520730</t>
+          <t>517509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>587523</t>
+          <t>586356</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>654234</t>
+          <t>650860</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>727159</t>
+          <t>724543</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84799</t>
+          <t>83669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115977</t>
+          <t>116347</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>388019</t>
+          <t>392657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>450681</t>
+          <t>456578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>481789</t>
+          <t>487521</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>552440</t>
+          <t>560033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108657</t>
+          <t>109508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150938</t>
+          <t>153627</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137687</t>
+          <t>137774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>185653</t>
+          <t>188060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1735369</t>
+          <t>1735324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1856081</t>
+          <t>1857035</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1775152</t>
+          <t>1774365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1897913</t>
+          <t>1897720</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3544779</t>
+          <t>3544008</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3720697</t>
+          <t>3725365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1133690</t>
+          <t>1129343</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1246788</t>
+          <t>1239960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1153635</t>
+          <t>1160672</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1272113</t>
+          <t>1275555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2320282</t>
+          <t>2317206</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2484469</t>
+          <t>2484521</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>391445</t>
+          <t>391999</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>473982</t>
+          <t>469133</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>445742</t>
+          <t>439958</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>528046</t>
+          <t>527161</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>856701</t>
+          <t>861442</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>979819</t>
+          <t>972257</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259960</t>
+          <t>263043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299712</t>
+          <t>302495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198610</t>
+          <t>198206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235040</t>
+          <t>235034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>468573</t>
+          <t>468614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524001</t>
+          <t>524079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77639</t>
+          <t>76895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115089</t>
+          <t>112353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60826</t>
+          <t>59945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91473</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147585</t>
+          <t>146770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197609</t>
+          <t>195239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68125</t>
+          <t>66421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40765</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67844</t>
+          <t>67626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>84475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>125609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215256</t>
+          <t>213862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252708</t>
+          <t>253522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>215996</t>
+          <t>214876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253990</t>
+          <t>253055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>441284</t>
+          <t>443949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495708</t>
+          <t>497312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84277</t>
+          <t>82681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117682</t>
+          <t>119970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>69347</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101083</t>
+          <t>102814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>160618</t>
+          <t>157909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>208828</t>
+          <t>207357</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54451</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>35350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64049</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72381</t>
+          <t>73619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110576</t>
+          <t>112365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314456</t>
+          <t>312541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>357664</t>
+          <t>356227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92397</t>
+          <t>90772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117851</t>
+          <t>115961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414656</t>
+          <t>414295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>464156</t>
+          <t>464790</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112901</t>
+          <t>112737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152710</t>
+          <t>152601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29171</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151645</t>
+          <t>150179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194964</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37956</t>
+          <t>37636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65739</t>
+          <t>63558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,47 +5346,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>71951</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>57345</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>90454</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>71951</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>56496</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>88817</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>715588</t>
+          <t>714720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>778412</t>
+          <t>779766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518892</t>
+          <t>518380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>574165</t>
+          <t>573958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1250833</t>
+          <t>1252382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1334756</t>
+          <t>1339854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251777</t>
+          <t>250814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>306906</t>
+          <t>307403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145100</t>
+          <t>145737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193695</t>
+          <t>193433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412698</t>
+          <t>408827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>486747</t>
+          <t>487407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99660</t>
+          <t>98434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140936</t>
+          <t>140788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89363</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130410</t>
+          <t>131922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>202440</t>
+          <t>201545</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>258430</t>
+          <t>260834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>387804</t>
+          <t>390977</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>436375</t>
+          <t>440402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>480687</t>
+          <t>477467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>532463</t>
+          <t>528956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>885589</t>
+          <t>883980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>954313</t>
+          <t>951145</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130502</t>
+          <t>129554</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>174431</t>
+          <t>173682</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141426</t>
+          <t>143936</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>189036</t>
+          <t>189705</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>284290</t>
+          <t>286548</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>349268</t>
+          <t>349622</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>39844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67156</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>50465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81769</t>
+          <t>81049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94494</t>
+          <t>96286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138316</t>
+          <t>137241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172559</t>
+          <t>172662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204620</t>
+          <t>205152</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>653012</t>
+          <t>661568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>720698</t>
+          <t>726988</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>843142</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>912678</t>
+          <t>914205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60879</t>
+          <t>61908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92454</t>
+          <t>93849</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>244355</t>
+          <t>240504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>304614</t>
+          <t>298095</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>316413</t>
+          <t>315446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>385502</t>
+          <t>379939</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,82 +6679,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>114446</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>93193</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>134678</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>132129</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>109701</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>157335</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>9,71%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>114446</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>95938</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>138089</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>132129</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>108827</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>154053</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2149740</t>
+          <t>2143924</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2268005</t>
+          <t>2260060</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2242280</t>
+          <t>2243687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2355312</t>
+          <t>2354567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4417786</t>
+          <t>4416331</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4579644</t>
+          <t>4579392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>780143</t>
+          <t>787199</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>883996</t>
+          <t>885880</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>753959</t>
+          <t>756802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>854065</t>
+          <t>855815</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1569314</t>
+          <t>1568919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1712956</t>
+          <t>1715006</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>298060</t>
+          <t>301377</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>367591</t>
+          <t>370625</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>371316</t>
+          <t>368767</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>452013</t>
+          <t>452288</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>690606</t>
+          <t>690256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>793474</t>
+          <t>793181</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>322037</t>
+          <t>322033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>365477</t>
+          <t>364031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290610</t>
+          <t>291125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>323897</t>
+          <t>325420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623745</t>
+          <t>623942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>679290</t>
+          <t>679301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80828</t>
+          <t>79851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118479</t>
+          <t>117058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68192</t>
+          <t>68496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94323</t>
+          <t>95398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156676</t>
+          <t>155620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201002</t>
+          <t>201408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49102</t>
+          <t>48957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79654</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46005</t>
+          <t>45032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73236</t>
+          <t>72318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>101322</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>141428</t>
+          <t>143256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>296801</t>
+          <t>297935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335803</t>
+          <t>335333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238851</t>
+          <t>238440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268735</t>
+          <t>269781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>546035</t>
+          <t>544677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>594142</t>
+          <t>595087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72780</t>
+          <t>73091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105975</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62900</t>
+          <t>62283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>87273</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141761</t>
+          <t>142044</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>184916</t>
+          <t>183599</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59779</t>
+          <t>61453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68605</t>
+          <t>68980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84750</t>
+          <t>84455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121658</t>
+          <t>120023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>461831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>624436</t>
+          <t>624451</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109009</t>
+          <t>110422</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128450</t>
+          <t>129126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>582200</t>
+          <t>584578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>767126</t>
+          <t>751702</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>49879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158543</t>
+          <t>155624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>15212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>76713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26878</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99747</t>
+          <t>100257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>771187</t>
+          <t>768014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>829598</t>
+          <t>824855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>729472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>875869</t>
+          <t>877409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1521387</t>
+          <t>1520262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1699272</t>
+          <t>1715100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137400</t>
+          <t>138477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>184568</t>
+          <t>188681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56433</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144575</t>
+          <t>146813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194117</t>
+          <t>185841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315510</t>
+          <t>314834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56440</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91515</t>
+          <t>90881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>40968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108315</t>
+          <t>106713</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107741</t>
+          <t>107387</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>183837</t>
+          <t>184550</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348764</t>
+          <t>349184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>386269</t>
+          <t>388041</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>642820</t>
+          <t>639460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>713535</t>
+          <t>712656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1004575</t>
+          <t>1002958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1087797</t>
+          <t>1088195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50663</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81140</t>
+          <t>81204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85315</t>
+          <t>87396</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135599</t>
+          <t>139771</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>146809</t>
+          <t>144699</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>209102</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>30764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55066</t>
+          <t>57255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>41258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>71183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78563</t>
+          <t>78147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117969</t>
+          <t>118933</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158108</t>
+          <t>159559</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>203832</t>
+          <t>202826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>558200</t>
+          <t>558009</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>604775</t>
+          <t>604460</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>731484</t>
+          <t>735149</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>794895</t>
+          <t>795662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56824</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104637</t>
+          <t>106180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143808</t>
+          <t>146185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133442</t>
+          <t>135427</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185937</t>
+          <t>186617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43088</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72287</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59218</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100062</t>
+          <t>102947</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2475169</t>
+          <t>2468002</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2757574</t>
+          <t>2738977</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2637863</t>
+          <t>2635220</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2879089</t>
+          <t>2866669</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5149294</t>
+          <t>5142902</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5517657</t>
+          <t>5536480</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>387000</t>
+          <t>403915</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>586886</t>
+          <t>589927</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>433895</t>
+          <t>438958</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>584310</t>
+          <t>588604</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>918263</t>
+          <t>911352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1145886</t>
+          <t>1145924</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>224650</t>
+          <t>229210</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>332962</t>
+          <t>333650</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>267521</t>
+          <t>269152</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>367417</t>
+          <t>369070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>530734</t>
+          <t>522312</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>682164</t>
+          <t>683234</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>192112</t>
+          <t>191124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236615</t>
+          <t>235675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140576</t>
+          <t>138955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177310</t>
+          <t>176286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344416</t>
+          <t>345666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401638</t>
+          <t>402543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136796</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181596</t>
+          <t>180411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129977</t>
+          <t>130091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243962</t>
+          <t>241443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300406</t>
+          <t>296498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49746</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80867</t>
+          <t>79643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>33319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59554</t>
+          <t>59494</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90044</t>
+          <t>88287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195622</t>
+          <t>196390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>237204</t>
+          <t>241935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146214</t>
+          <t>143436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185171</t>
+          <t>181918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349302</t>
+          <t>350824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>408244</t>
+          <t>409147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131714</t>
+          <t>131241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172042</t>
+          <t>174686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98575</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>134768</t>
+          <t>137495</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>241302</t>
+          <t>240361</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>300652</t>
+          <t>298032</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>64987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>41020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70140</t>
+          <t>69281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87166</t>
+          <t>86075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126108</t>
+          <t>128817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301195</t>
+          <t>298345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>350981</t>
+          <t>349210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121495</t>
+          <t>120995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154789</t>
+          <t>154179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>433739</t>
+          <t>432616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>493842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182212</t>
+          <t>182869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229559</t>
+          <t>229199</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62497</t>
+          <t>63144</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94138</t>
+          <t>94433</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257006</t>
+          <t>253370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314235</t>
+          <t>313168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79441</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120175</t>
+          <t>118912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30733</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>55274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116290</t>
+          <t>118470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161527</t>
+          <t>163124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>572610</t>
+          <t>574247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>640429</t>
+          <t>648578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>368250</t>
+          <t>370572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>426739</t>
+          <t>426978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>960093</t>
+          <t>961322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1053085</t>
+          <t>1048300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>378155</t>
+          <t>373652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>442055</t>
+          <t>444189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231052</t>
+          <t>231958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>286019</t>
+          <t>283053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>623576</t>
+          <t>621713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>709395</t>
+          <t>713067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113606</t>
+          <t>111131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>161290</t>
+          <t>159432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>91505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132077</t>
+          <t>131125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215057</t>
+          <t>216167</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>273993</t>
+          <t>277581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271248</t>
+          <t>270729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316006</t>
+          <t>316020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>394099</t>
+          <t>395989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>451397</t>
+          <t>451989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>681031</t>
+          <t>678940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>758020</t>
+          <t>751000</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141783</t>
+          <t>143357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184363</t>
+          <t>185604</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>205943</t>
+          <t>201991</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>260708</t>
+          <t>254970</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>356986</t>
+          <t>358683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>425789</t>
+          <t>428164</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40155</t>
+          <t>39946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67269</t>
+          <t>67697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83973</t>
+          <t>86537</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123375</t>
+          <t>123592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134472</t>
+          <t>135316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>181656</t>
+          <t>182266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117310</t>
+          <t>118171</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149814</t>
+          <t>149899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>517509</t>
+          <t>519887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>586356</t>
+          <t>586168</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>650860</t>
+          <t>650285</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>724543</t>
+          <t>725257</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83669</t>
+          <t>84040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116347</t>
+          <t>114462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>392657</t>
+          <t>389386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>456578</t>
+          <t>456311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>487521</t>
+          <t>485149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>560033</t>
+          <t>557015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109508</t>
+          <t>109593</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153627</t>
+          <t>152854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137774</t>
+          <t>139791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188060</t>
+          <t>187793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1735324</t>
+          <t>1733450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1857035</t>
+          <t>1856987</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1774365</t>
+          <t>1774671</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1897720</t>
+          <t>1890411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3544008</t>
+          <t>3536954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3725365</t>
+          <t>3712833</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1129343</t>
+          <t>1131357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1239960</t>
+          <t>1245041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1160672</t>
+          <t>1156608</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1275555</t>
+          <t>1271938</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2317206</t>
+          <t>2325071</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2484521</t>
+          <t>2492440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>391999</t>
+          <t>394054</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>469133</t>
+          <t>471275</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>439958</t>
+          <t>442734</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>527161</t>
+          <t>525779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>861442</t>
+          <t>861077</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>972257</t>
+          <t>977698</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>263043</t>
+          <t>260118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302495</t>
+          <t>301286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198206</t>
+          <t>197234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235034</t>
+          <t>232977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>468614</t>
+          <t>468535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524079</t>
+          <t>522754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76895</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112353</t>
+          <t>112592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>58445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91676</t>
+          <t>92154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146770</t>
+          <t>148670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195239</t>
+          <t>196141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40847</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67626</t>
+          <t>67130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>128298</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213862</t>
+          <t>215286</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253522</t>
+          <t>252699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214876</t>
+          <t>214560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253055</t>
+          <t>252593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>443949</t>
+          <t>440768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>497312</t>
+          <t>495062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82681</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119970</t>
+          <t>118358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69347</t>
+          <t>69974</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>103593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157909</t>
+          <t>160835</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>207357</t>
+          <t>207928</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>31698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35350</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>63598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73619</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112365</t>
+          <t>109490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>312541</t>
+          <t>313469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>356227</t>
+          <t>358058</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90772</t>
+          <t>92038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115961</t>
+          <t>117060</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414295</t>
+          <t>414467</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>464790</t>
+          <t>466985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112737</t>
+          <t>112017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152601</t>
+          <t>154019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>51106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150179</t>
+          <t>149795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195270</t>
+          <t>196226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37636</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63558</t>
+          <t>66277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57345</t>
+          <t>57012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>714720</t>
+          <t>714152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>779766</t>
+          <t>781992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518380</t>
+          <t>518574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>573958</t>
+          <t>572376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1252382</t>
+          <t>1254096</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1339854</t>
+          <t>1338046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250814</t>
+          <t>248849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>307403</t>
+          <t>309008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145737</t>
+          <t>147767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193433</t>
+          <t>194078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>408827</t>
+          <t>412618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>487407</t>
+          <t>487904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98434</t>
+          <t>100719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140788</t>
+          <t>142737</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89425</t>
+          <t>91326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131922</t>
+          <t>130828</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>201545</t>
+          <t>199352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>260834</t>
+          <t>258967</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>390977</t>
+          <t>391222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>440402</t>
+          <t>437105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>528956</t>
+          <t>529886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>883980</t>
+          <t>889787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>951145</t>
+          <t>955705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>129554</t>
+          <t>130142</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173682</t>
+          <t>172486</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>143936</t>
+          <t>144449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>189705</t>
+          <t>188390</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>286548</t>
+          <t>281451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>349622</t>
+          <t>345913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39844</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67793</t>
+          <t>67500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>49158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81049</t>
+          <t>80073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96286</t>
+          <t>96576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137241</t>
+          <t>137948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172662</t>
+          <t>170494</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>205152</t>
+          <t>203116</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>661568</t>
+          <t>661757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>726988</t>
+          <t>725660</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>843142</t>
+          <t>842154</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>914205</t>
+          <t>917337</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61908</t>
+          <t>63298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93849</t>
+          <t>94780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240504</t>
+          <t>241796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>298095</t>
+          <t>297348</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>315446</t>
+          <t>315628</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>379939</t>
+          <t>381615</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>93541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134678</t>
+          <t>138595</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109701</t>
+          <t>112247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>157335</t>
+          <t>159384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2143924</t>
+          <t>2145649</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2260060</t>
+          <t>2262042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2243687</t>
+          <t>2239285</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2354567</t>
+          <t>2356558</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4416331</t>
+          <t>4427151</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4579392</t>
+          <t>4582628</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>787199</t>
+          <t>782978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>885880</t>
+          <t>884168</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>756802</t>
+          <t>754756</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>855815</t>
+          <t>856726</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1568919</t>
+          <t>1566770</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1715006</t>
+          <t>1703498</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>301377</t>
+          <t>298975</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>370625</t>
+          <t>371217</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>368767</t>
+          <t>370765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>452288</t>
+          <t>447532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>690256</t>
+          <t>695265</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>793181</t>
+          <t>801647</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -7579,32 +7579,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>344219</t>
+          <t>378738</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>322033</t>
+          <t>358346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>364031</t>
+          <t>403310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7614,32 +7614,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>307759</t>
+          <t>333769</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291125</t>
+          <t>314871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>325420</t>
+          <t>351318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7649,32 +7649,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>651979</t>
+          <t>712507</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>681666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>679301</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97883</t>
+          <t>105105</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79851</t>
+          <t>87831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>125051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>87509</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>74429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95398</t>
+          <t>101988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7762,32 +7762,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>178194</t>
+          <t>192614</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155620</t>
+          <t>169008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201408</t>
+          <t>217809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>66775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>51445</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>63299</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45032</t>
+          <t>50663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>79821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>130074</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102503</t>
+          <t>110728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>143256</t>
+          <t>155411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -7918,17 +7918,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>445961</t>
+          <t>484577</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>445961</t>
+          <t>484577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>445961</t>
+          <t>484577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951174</t>
+          <t>1035195</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951174</t>
+          <t>1035195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951174</t>
+          <t>1035195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>317909</t>
+          <t>339151</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297935</t>
+          <t>317542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335333</t>
+          <t>358039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>253897</t>
+          <t>279041</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238440</t>
+          <t>262336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>269781</t>
+          <t>296055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8105,32 +8105,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>571807</t>
+          <t>618192</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>544677</t>
+          <t>588472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>595087</t>
+          <t>644196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -8148,32 +8148,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88037</t>
+          <t>94987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73091</t>
+          <t>78650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8183,32 +8183,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73652</t>
+          <t>85642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62283</t>
+          <t>72686</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>99836</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8218,32 +8218,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>161689</t>
+          <t>180629</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>142044</t>
+          <t>157971</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>183599</t>
+          <t>205193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35001</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61453</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68980</t>
+          <t>71052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101298</t>
+          <t>107533</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>91198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120023</t>
+          <t>128043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -8374,17 +8374,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8409,17 +8409,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8491,32 +8491,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>544063</t>
+          <t>332487</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>461831</t>
+          <t>310186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>624451</t>
+          <t>352321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8526,32 +8526,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119624</t>
+          <t>134284</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110422</t>
+          <t>123955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129126</t>
+          <t>144123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663687</t>
+          <t>466771</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>584578</t>
+          <t>439165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>751702</t>
+          <t>489630</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -8604,32 +8604,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>90135</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>72849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>109295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8639,32 +8639,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34822</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8674,32 +8674,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>106201</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49879</t>
+          <t>100713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155624</t>
+          <t>142275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -8717,32 +8717,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44161</t>
+          <t>48990</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76713</t>
+          <t>65390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8752,32 +8752,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21125</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8787,32 +8787,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>65287</t>
+          <t>73186</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -8830,17 +8830,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8865,17 +8865,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8947,32 +8947,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>799571</t>
+          <t>853083</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>768014</t>
+          <t>820831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>824855</t>
+          <t>883695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8982,32 +8982,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>786113</t>
+          <t>640723</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>729472</t>
+          <t>618963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>877409</t>
+          <t>661759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9017,32 +9017,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1585685</t>
+          <t>1493807</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1520262</t>
+          <t>1453542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1715100</t>
+          <t>1531551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -9060,32 +9060,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160884</t>
+          <t>190681</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138477</t>
+          <t>165551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188681</t>
+          <t>220271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>110656</t>
+          <t>124471</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59202</t>
+          <t>106159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146813</t>
+          <t>143683</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9130,32 +9130,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>271540</t>
+          <t>315152</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185841</t>
+          <t>283668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314834</t>
+          <t>347211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -9173,32 +9173,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72642</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57402</t>
+          <t>67419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90881</t>
+          <t>105354</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9208,32 +9208,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81165</t>
+          <t>95307</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40968</t>
+          <t>80528</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106713</t>
+          <t>113464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>153806</t>
+          <t>180630</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107387</t>
+          <t>159591</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184550</t>
+          <t>208449</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -9286,17 +9286,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033097</t>
+          <t>1129086</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033097</t>
+          <t>1129086</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033097</t>
+          <t>1129086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9321,17 +9321,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977934</t>
+          <t>860502</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977934</t>
+          <t>860502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977934</t>
+          <t>860502</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2011031</t>
+          <t>1989589</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2011031</t>
+          <t>1989589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2011031</t>
+          <t>1989589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9403,32 +9403,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>368927</t>
+          <t>442507</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349184</t>
+          <t>421406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>388041</t>
+          <t>461342</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>669122</t>
+          <t>634879</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>639460</t>
+          <t>614897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>712656</t>
+          <t>654552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9473,32 +9473,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1038049</t>
+          <t>1077386</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1002958</t>
+          <t>1048968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1088195</t>
+          <t>1106372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -9516,32 +9516,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64548</t>
+          <t>76335</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50315</t>
+          <t>60987</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81204</t>
+          <t>94069</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9551,32 +9551,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115988</t>
+          <t>129996</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87396</t>
+          <t>112534</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>139771</t>
+          <t>149474</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9586,32 +9586,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>180536</t>
+          <t>206331</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144699</t>
+          <t>179667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208473</t>
+          <t>229004</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -9629,32 +9629,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>49122</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>36737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>65717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9664,32 +9664,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>65975</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71183</t>
+          <t>79416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9699,32 +9699,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>97796</t>
+          <t>115096</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78147</t>
+          <t>97413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118933</t>
+          <t>134435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -9742,17 +9742,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9812,17 +9812,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>182934</t>
+          <t>180742</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>159559</t>
+          <t>159561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>202826</t>
+          <t>199371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9894,32 +9894,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>581367</t>
+          <t>641842</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>558009</t>
+          <t>614970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>604460</t>
+          <t>665717</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>764301</t>
+          <t>822584</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>735149</t>
+          <t>787844</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>795662</t>
+          <t>851815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -9972,32 +9972,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35119</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>53743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10007,32 +10007,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>123661</t>
+          <t>138744</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106180</t>
+          <t>117423</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146185</t>
+          <t>161584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>158780</t>
+          <t>172480</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135427</t>
+          <t>146817</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186617</t>
+          <t>203418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -10085,32 +10085,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43930</t>
+          <t>41386</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10120,32 +10120,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>55812</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72633</t>
+          <t>80879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>85852</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102947</t>
+          <t>110684</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -10198,17 +10198,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760840</t>
+          <t>843688</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760840</t>
+          <t>843688</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760840</t>
+          <t>843688</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001347</t>
+          <t>1080916</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001347</t>
+          <t>1080916</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001347</t>
+          <t>1080916</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10315,32 +10315,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2557624</t>
+          <t>2526706</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2468002</t>
+          <t>2469540</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2738977</t>
+          <t>2585051</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10350,32 +10350,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2717882</t>
+          <t>2664540</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2635220</t>
+          <t>2619887</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2866669</t>
+          <t>2720398</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10385,32 +10385,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5275506</t>
+          <t>5191246</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5142902</t>
+          <t>5119412</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5536480</t>
+          <t>5264844</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -10428,32 +10428,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>526509</t>
+          <t>590978</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>403915</t>
+          <t>541680</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>589927</t>
+          <t>642107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10463,32 +10463,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>530430</t>
+          <t>595380</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>438958</t>
+          <t>550409</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>588604</t>
+          <t>635078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10498,32 +10498,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1056939</t>
+          <t>1186359</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>911352</t>
+          <t>1128322</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1145924</t>
+          <t>1250034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -10541,32 +10541,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>290206</t>
+          <t>322034</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>229210</t>
+          <t>286953</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>333650</t>
+          <t>362338</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10576,32 +10576,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>327249</t>
+          <t>370338</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>269152</t>
+          <t>337493</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>369070</t>
+          <t>405199</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>617455</t>
+          <t>692372</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>522312</t>
+          <t>644674</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>683234</t>
+          <t>738042</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -10654,17 +10654,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3374339</t>
+          <t>3439719</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3374339</t>
+          <t>3439719</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3374339</t>
+          <t>3439719</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3575561</t>
+          <t>3630258</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3575561</t>
+          <t>3630258</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3575561</t>
+          <t>3630258</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10724,17 +10724,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6949900</t>
+          <t>7069977</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6949900</t>
+          <t>7069977</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6949900</t>
+          <t>7069977</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
